--- a/Interview questions.xlsx
+++ b/Interview questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Testing\Interview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EE8475-58A1-4FF9-8EBE-E23682722F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0EBE63-7BE9-4985-87B0-7EEEAB2A6DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Playwright Basics" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,11 @@
     <sheet name="UI Automation" sheetId="7" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="8" r:id="rId7"/>
     <sheet name="API" sheetId="11" r:id="rId8"/>
+    <sheet name="Common Questions" sheetId="12" r:id="rId9"/>
+    <sheet name="Testing" sheetId="13" r:id="rId10"/>
+    <sheet name="Git" sheetId="14" r:id="rId11"/>
+    <sheet name="CICD" sheetId="15" r:id="rId12"/>
+    <sheet name="Sheet5" sheetId="16" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Locators!$A$1:$D$42</definedName>
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="177">
   <si>
     <t>No</t>
   </si>
@@ -391,183 +396,6 @@
   </si>
   <si>
     <t>In Playwright, you configure default wait times in playwright.config.ts using actionTimeout, expect.timeout, or the global timeout for tests. This way you don’t need to set timeouts manually in every test.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByRole()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements using their accessibility role (button, textbox, checkbox, link, heading, etc.).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByText()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements based on visible text.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByLabel()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates form fields using their label text..
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByPlaceholder()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates inputs by their placeholder attribute.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByAltText()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements (usually images) by their alt text.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByTitle()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements by their title attribute.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByTestId()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements by a data-testid attribute.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>locator()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Generic locator that can use CSS selectors, XPath, and data attributes.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1601,19 +1429,6 @@
     <t>Page methods()</t>
   </si>
   <si>
-    <t>page.goto(url) → Navigate to a URL
-page.reload() → Reload the current page
-page.goBack() → Navigate back in history
-page.goForward() → Navigate forward in history
-page.title() → Get the page title
-page.url() → Get the current page URL
-page.content() → Get the full HTML content of the page
-page.setContent(html) → Set the page content directly
-page.evaluate(fn, arg) → Run JavaScript in the page context
-page.pdf(options) → Generate a PDF of the page (Chromium only)
-page.waitForSelector(selector) → Wait until an element appears</t>
-  </si>
-  <si>
     <t>Download Files</t>
   </si>
   <si>
@@ -1731,9 +1546,6 @@
   </si>
   <si>
     <t>iFrames</t>
-  </si>
-  <si>
-    <t xml:space="preserve">popup, dialog, alert, </t>
   </si>
   <si>
     <t>What's ARIA?</t>
@@ -2799,10 +2611,7 @@
     </r>
   </si>
   <si>
-    <t>Questions I still have</t>
-  </si>
-  <si>
-    <t>how do we use this to upload file??????</t>
+    <t>Opening new empty tab</t>
   </si>
   <si>
     <r>
@@ -2902,8 +2711,956 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.locator('h1')).toHaveText('Welcome to Popup');
+      <t>.locator('h1')).toHaveText('Welcome');
 });</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Page object represents a browser tab. I can create a new page using context.newPage(), navigate it with page.goto(), and then interact with elements using locators and assertions
+import {test} from '@plawyright/test'
+test('Opening Empty tabs', async({browser})=&gt;{
+const context = await browser.newContext();
+const page = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>await context.newPage()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;
+await page.goto('https://example.com');
+});</t>
+    </r>
+  </si>
+  <si>
+    <t>How to handle Alert?</t>
+  </si>
+  <si>
+    <t>How to handle multiple Alert?</t>
+  </si>
+  <si>
+    <t>// Global listener: catches all alerts
+page.on('dialog', async dialog =&gt; {
+  console.log('Alert text:', dialog.message());
+  // Example: accept the first, dismiss the second
+  if (dialog.message().includes('First')) {
+    await dialog.accept();
+  } else {
+    await dialog.dismiss();
+  }
+});
+---------------------------------------------------------------------------------------------------------------------------------------------------------------
+// Handle first alert
+const firstDialog = await page.waitForEvent('dialog');
+console.log('First alert:', firstDialog.message());
+await firstDialog.accept();
+// Handle second alert
+const secondDialog = await page.waitForEvent('dialog');
+console.log('Second alert:', secondDialog.message());
+await secondDialog.dismiss();</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Playwright gives me two ways to handle alerts. With </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.on('dialog')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, I set up a global listener that catches all alerts, and I can add conditional logic — for example, accept the first alert but dismiss the second. With </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.waitForEvent('dialog')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, I handle one alert at a specific step. The difference is that the listener is global and reusable, while waitForEvent is precise and one‑time.
+page.on('dialog', async dialog =&gt; {
+  console.log('Alert text:', dialog.message());
+  await dialog.accept();
+}
+const alertEvent = await page.waitForEvent('dialog');
+await page.getByRole('button', {name : 'submit'}).click();
+const  alert=await alertEvent;
+await alert.accept();
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByRole()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements using their accessibility role (button, textbox, checkbox, link, heading, etc.).
+page.getByRole('button', { name: 'Submit' })
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByText()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements based on visible text.
+page.getByText('Welcome back!')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByLabel()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates form fields using their label text.
+page.getByLabel('Email address')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByPlaceholder()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates inputs by their placeholder attribute.
+page.getByPlaceholder('Enter your password')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByAltText()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements (usually images) by their alt text.
+page.getByAltText('Company logo')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByTitle()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements by their title attribute.
+page.getByTitle('Close')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByTestId()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements by a data-testid attribute.
+page.getByTestId('login-button')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>locator()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Generic locator that can use CSS selectors, XPath, and data attributes.
+page.locator('//input[@name="username"]')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.goto(url)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Navigate to a URL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.reload()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Reload the current page
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.goBack()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Navigate back in history
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.goForward()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Navigate forward in history
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.title()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Get the page title
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.url()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Get the current page URL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.content()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Get the full HTML content of the page
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">page.setContent(html) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">→ Set the page content directly
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.evaluate(fn, arg)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Run JavaScript in the page context
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.pdf(options)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Generate a PDF of the page (Chromium only)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.waitForSelector(selector)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Wait until an element appears</t>
+    </r>
+  </si>
+  <si>
+    <t>Button appears after 10 seconds</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>explicit waits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (WebDriverWait in Selenium / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>page.waitForSelector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Playwright) to wait until the button is visible and enabled before interacting. Avoid hard sleeps.</t>
+    </r>
+  </si>
+  <si>
+    <t>Spinner disappears</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wait for the spinner element to become </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hidden or detached</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>waitForSelector('.spinner', { state: 'hidden' })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. This ensures the page is ready for next action.</t>
+    </r>
+  </si>
+  <si>
+    <t>Multiple tabs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Handle via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>context switching</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. In Selenium: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>driver.switchTo().window(handle)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. In Playwright: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>context.newPage()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>browserContext.pages()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Always track handles/pages.</t>
+    </r>
+  </si>
+  <si>
+    <t>Multiple users</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Simulate with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>multiple browser contexts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Each context has isolated cookies/storage. In Playwright: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>browser.newContext()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. In Selenium: launch separate driver instances.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dynamic tables</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Identify rows/columns dynamically. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>XPath/CSS with contains() or nth-child</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Iterate through rows, match cell text, then perform action on sibling/child element.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dynamic XPath</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>functions like contains(), starts-with(), normalize-space()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to handle changing attributes. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>//button[contains(text(),'Submit')]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Avoid brittle absolute paths.</t>
+    </r>
+  </si>
+  <si>
+    <t>Infinite scrolling</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scroll automation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> until no new elements load. In Playwright: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>page.evaluate(() =&gt; window.scrollBy(0, document.body.scrollHeight))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in a loop with waits.</t>
+    </r>
+  </si>
+  <si>
+    <t>Date picker</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Interact by sending date string if input allows. If custom UI, locate calendar cells and click dynamically. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>attribute-based locators</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for day/month/year.</t>
+    </r>
+  </si>
+  <si>
+    <t>Calendar handling</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Handle navigation (next/prev month) and select specific dates. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>parameterized locators</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for day values. For range selection, click start date then end date.</t>
     </r>
   </si>
 </sst>
@@ -2911,7 +3668,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2950,6 +3707,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2965,7 +3727,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2986,17 +3748,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -3035,20 +3786,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3336,7 +4087,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="9"/>
     <col min="2" max="2" width="46.81640625" style="9" customWidth="1"/>
@@ -3345,7 +4096,7 @@
     <col min="5" max="16384" width="8.7265625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3357,7 +4108,7 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="87">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3368,7 +4119,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="43.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3376,10 +4127,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="72.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3387,10 +4138,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="58">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3398,10 +4149,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3412,7 +4163,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="43.5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3423,7 +4174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3434,7 +4185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="72.5" customHeight="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3442,10 +4193,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="81" customHeight="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3453,21 +4204,21 @@
         <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="43.5">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="43.5">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3478,7 +4229,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="43.5">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -3489,18 +4240,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:4" ht="72.5">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3508,10 +4259,10 @@
         <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="29">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3522,7 +4273,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="43.5">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3533,7 +4284,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="43.5">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3544,20 +4295,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="7" t="s">
+    <row r="19" spans="1:3" ht="43.5">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="43.5">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3566,10 +4323,46 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD767E3-2E90-46E1-B9AD-5D1949795010}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52649227-AF6C-46D2-902A-33B4D9B84B9E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFB5C7D-92B8-4C6A-8BCF-8D1BE6F73F71}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975AD39B-1C4B-4DE0-8AD9-C324340E2C67}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{913B1BA8-DC3A-4E90-879B-767360794D4C}">
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="9"/>
     <col min="2" max="2" width="46.81640625" style="9" customWidth="1"/>
@@ -3578,7 +4371,7 @@
     <col min="5" max="16384" width="8.7265625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3588,12 +4381,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+      <c r="D1"/>
+    </row>
+    <row r="2" spans="1:4" customFormat="1" ht="58">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3603,8 +4394,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
+    <row r="3" spans="1:4" customFormat="1" ht="58">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -3614,19 +4405,19 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:4" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
+    <row r="4" spans="1:4" customFormat="1" ht="232">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" customFormat="1" ht="58">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -3636,8 +4427,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
+    <row r="6" spans="1:4" customFormat="1" ht="58">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3647,19 +4438,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="12">
+    <row r="7" spans="1:4" customFormat="1" ht="43.5">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" customFormat="1" ht="29">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -3669,19 +4460,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:4" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A9" s="12">
+    <row r="9" spans="1:4" customFormat="1" ht="174">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="12">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" customFormat="1" ht="29">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3691,8 +4482,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+    <row r="11" spans="1:4" customFormat="1" ht="43.5">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -3702,30 +4493,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A12" s="12">
+    <row r="12" spans="1:4" customFormat="1" ht="58">
+      <c r="A12" s="11">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:4" customFormat="1" ht="188.5">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="12">
+    </row>
+    <row r="14" spans="1:4" customFormat="1" ht="43.5">
+      <c r="A14" s="11">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3735,8 +4526,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
+    <row r="15" spans="1:4" customFormat="1" ht="43.5">
+      <c r="A15" s="11">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3746,8 +4537,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="12">
+    <row r="16" spans="1:4" customFormat="1">
+      <c r="A16" s="11">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -3757,22 +4548,19 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12">
+    <row r="17" spans="1:3" ht="188.5">
+      <c r="A17" s="11">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="12">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" customFormat="1">
+      <c r="A18" s="11">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -3782,19 +4570,19 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A19" s="12">
+    <row r="19" spans="1:3" customFormat="1" ht="58">
+      <c r="A19" s="11">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
+    </row>
+    <row r="20" spans="1:3" customFormat="1" ht="43.5">
+      <c r="A20" s="11">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -3804,19 +4592,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="12">
+    <row r="21" spans="1:3" customFormat="1" ht="72.5">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="12">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" customFormat="1" ht="29">
+      <c r="A22" s="11">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -3826,8 +4614,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="12">
+    <row r="23" spans="1:3" customFormat="1" ht="29">
+      <c r="A23" s="11">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3837,8 +4625,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="12">
+    <row r="24" spans="1:3" customFormat="1" ht="29">
+      <c r="A24" s="11">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3848,8 +4636,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="12">
+    <row r="25" spans="1:3" customFormat="1" ht="29">
+      <c r="A25" s="11">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -3859,8 +4647,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
+    <row r="26" spans="1:3" customFormat="1" ht="43.5">
+      <c r="A26" s="11">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -3870,8 +4658,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="12">
+    <row r="27" spans="1:3" customFormat="1" ht="43.5">
+      <c r="A27" s="11">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -3881,8 +4669,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="12">
+    <row r="28" spans="1:3" customFormat="1" ht="29">
+      <c r="A28" s="11">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -3892,8 +4680,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
+    <row r="29" spans="1:3" customFormat="1" ht="29">
+      <c r="A29" s="11">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -3903,8 +4691,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
+    <row r="30" spans="1:3" customFormat="1" ht="29">
+      <c r="A30" s="11">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -3914,8 +4702,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
+    <row r="31" spans="1:3" customFormat="1" ht="43.5">
+      <c r="A31" s="11">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -3925,19 +4713,19 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
+    <row r="32" spans="1:3" customFormat="1" ht="29">
+      <c r="A32" s="11">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" customFormat="1" ht="58">
+      <c r="A33" s="11">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -3947,8 +4735,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
+    <row r="34" spans="1:3" customFormat="1" ht="29">
+      <c r="A34" s="11">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -3958,8 +4746,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="35" spans="1:3" customFormat="1">
+      <c r="A35" s="11">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -3969,8 +4757,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="36" spans="1:3" customFormat="1" ht="43.5">
+      <c r="A36" s="11">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -3980,8 +4768,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="1:3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
+    <row r="37" spans="1:3" customFormat="1" ht="43.5">
+      <c r="A37" s="11">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -3991,8 +4779,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
+    <row r="38" spans="1:3" customFormat="1" ht="43.5">
+      <c r="A38" s="11">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -4002,8 +4790,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="12">
+    <row r="39" spans="1:3" customFormat="1" ht="72.5">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -4013,35 +4801,29 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
+    <row r="40" spans="1:3" customFormat="1">
+      <c r="A40" s="11">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" customFormat="1" ht="217.5">
+      <c r="A41" s="11">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="12">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="14">
-        <v>41</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D42" xr:uid="{913B1BA8-DC3A-4E90-879B-767360794D4C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4049,14 +4831,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89D32A3-AD28-4D58-95C3-DE837C529693}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
     <col min="3" max="3" width="102.26953125" customWidth="1"/>
     <col min="4" max="4" width="61.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4068,15 +4850,15 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" ht="232" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+    <row r="2" spans="1:4" ht="232">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -4087,15 +4869,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B9138F-152F-47B5-A715-13A6525B10BB}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
     <col min="3" max="3" width="102.26953125" customWidth="1"/>
     <col min="4" max="4" width="61.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" s="8" customFormat="1">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -4106,19 +4888,19 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+    <row r="2" spans="1:4" ht="87">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="29">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -4128,8 +4910,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
+    <row r="4" spans="1:4" ht="43.5">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -4139,8 +4921,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
+    <row r="5" spans="1:4" ht="29">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -4150,15 +4932,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="232" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
+    <row r="6" spans="1:4" ht="232">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>145</v>
+        <v>130</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4169,14 +4951,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0E38E55-F52F-47EC-A591-5E37D8DFD2A5}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
     <col min="3" max="3" width="102.26953125" customWidth="1"/>
     <col min="4" max="4" width="61.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4188,15 +4970,15 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+    <row r="2" spans="1:4" ht="159.5">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -4206,15 +4988,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6422BD2A-921C-4791-9418-7944EF57C8A1}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
     <col min="3" max="3" width="102.26953125" customWidth="1"/>
     <col min="4" max="4" width="61.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4226,73 +5008,103 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" ht="261" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+    <row r="2" spans="1:4" ht="261">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="130.5">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="87">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.5">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="87">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="290">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="174">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="217.5">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="319">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A5" s="12"/>
-      <c r="B5" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="290" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="174" x14ac:dyDescent="0.35">
-      <c r="A7" s="12">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="11" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4302,15 +5114,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308F6E79-B2D5-41F4-AD37-A7BE9FF5DB5F}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
     <col min="3" max="3" width="102.26953125" customWidth="1"/>
     <col min="4" max="4" width="61.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4322,8 +5134,8 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" ht="145" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+    <row r="2" spans="1:4" ht="145">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -4333,8 +5145,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="116" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
+    <row r="3" spans="1:4" ht="116">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -4344,8 +5156,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
+    <row r="4" spans="1:4" ht="87">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -4353,6 +5165,105 @@
       </c>
       <c r="C4" s="4" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="29">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="29">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="29">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="29">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="29">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4363,7 +5274,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81243443-8543-49DE-8D13-ABDA6A090A9E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF8916E-9B29-4465-A07F-359CF4171505}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Interview questions.xlsx
+++ b/Interview questions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Testing\Interview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonlinenam-my.sharepoint.com/personal/910388_cognizant_com/Documents/Desktop/Playwright/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0EBE63-7BE9-4985-87B0-7EEEAB2A6DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{AC0EBE63-7BE9-4985-87B0-7EEEAB2A6DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04903C3E-5143-4B8F-9C4B-1B8831347FB6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Playwright Basics" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="179">
   <si>
     <t>No</t>
   </si>
@@ -321,9 +321,6 @@
   </si>
   <si>
     <t>What is the difference between: await expect(locator).toBeVisible(); and await locator.isVisible(); When would you use each?</t>
-  </si>
-  <si>
-    <t>difference between : test.only(),  test.skip(), test.fail() and test.fixme()</t>
   </si>
   <si>
     <t>ischecked return true/false and you need to handle the result in separate code.
@@ -868,74 +865,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">In Playwright, there is no switchToWindow() method like in Selenium. Each browser tab is represented by a Page object. For existing tabs, we can get all open pages using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>context.pages()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and then interact with the required page object directly or bring it to the front using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bringToFront()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Now, context.pages().length only tells you how many tabs are open, like 12, but you can’t switch just by knowing the number. To actually switch, you loop through the pages, check each tab’s URL with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.url()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and when you find the one you want, you call bringToFront(). So the number is just a count, but page.url() helps identify the right tab to switch to.”</t>
-    </r>
-  </si>
-  <si>
     <t>test.describe() in Playwright is used to group related tests together under a common block.
 It helps organize tests logically (e.g., all login tests, all checkout tests).
 You can apply hooks (beforeAll, afterAll, beforeEach, afterEach) inside a describe block so they only affect the tests within that group.</t>
@@ -2249,79 +2178,6 @@
   <si>
     <t>Hard asserts stop execution immediately when they fail, while soft asserts allow the test to continue and collect all failures, reporting them at the end. Hard asserts are used for critical checks, soft asserts for comprehensive validations.
 Playwright uses hard assertions by default.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">storageState is used to save and reuse browser authentication state, including cookies and local storage data. It helps avoid repeated logins and speeds up test execution.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Save the state after login</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : await page.context().</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>storageState</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">({ path: 'auth.json' });
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Reuse the state in new tests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 
-const context = await browser.newContext({ storageState: 'auth.json' });
-const page = await context.newPage();
-await page.goto('https://example.com/dashboard'); // already logged in</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2776,6 +2632,1016 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByRole()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements using their accessibility role (button, textbox, checkbox, link, heading, etc.).
+page.getByRole('button', { name: 'Submit' })
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByText()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements based on visible text.
+page.getByText('Welcome back!')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByLabel()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates form fields using their label text.
+page.getByLabel('Email address')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByPlaceholder()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates inputs by their placeholder attribute.
+page.getByPlaceholder('Enter your password')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByAltText()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements (usually images) by their alt text.
+page.getByAltText('Company logo')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByTitle()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements by their title attribute.
+page.getByTitle('Close')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getByTestId()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Locates elements by a data-testid attribute.
+page.getByTestId('login-button')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>locator()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Generic locator that can use CSS selectors, XPath, and data attributes.
+page.locator('//input[@name="username"]')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.goto(url)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Navigate to a URL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.reload()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Reload the current page
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.goBack()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Navigate back in history
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.goForward()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Navigate forward in history
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.title()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Get the page title
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.url()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Get the current page URL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.content()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Get the full HTML content of the page
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">page.setContent(html) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">→ Set the page content directly
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.evaluate(fn, arg)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Run JavaScript in the page context
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.pdf(options)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Generate a PDF of the page (Chromium only)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.waitForSelector(selector)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Wait until an element appears</t>
+    </r>
+  </si>
+  <si>
+    <t>Button appears after 10 seconds</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>explicit waits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (WebDriverWait in Selenium / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>page.waitForSelector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Playwright) to wait until the button is visible and enabled before interacting. Avoid hard sleeps.</t>
+    </r>
+  </si>
+  <si>
+    <t>Spinner disappears</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wait for the spinner element to become </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hidden or detached</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>waitForSelector('.spinner', { state: 'hidden' })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. This ensures the page is ready for next action.</t>
+    </r>
+  </si>
+  <si>
+    <t>Multiple tabs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Handle via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>context switching</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. In Selenium: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>driver.switchTo().window(handle)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. In Playwright: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>context.newPage()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>browserContext.pages()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Always track handles/pages.</t>
+    </r>
+  </si>
+  <si>
+    <t>Multiple users</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Simulate with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>multiple browser contexts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Each context has isolated cookies/storage. In Playwright: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>browser.newContext()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. In Selenium: launch separate driver instances.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dynamic tables</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Identify rows/columns dynamically. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>XPath/CSS with contains() or nth-child</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Iterate through rows, match cell text, then perform action on sibling/child element.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dynamic XPath</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>functions like contains(), starts-with(), normalize-space()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to handle changing attributes. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>//button[contains(text(),'Submit')]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Avoid brittle absolute paths.</t>
+    </r>
+  </si>
+  <si>
+    <t>Infinite scrolling</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scroll automation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> until no new elements load. In Playwright: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>page.evaluate(() =&gt; window.scrollBy(0, document.body.scrollHeight))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in a loop with waits.</t>
+    </r>
+  </si>
+  <si>
+    <t>Date picker</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Interact by sending date string if input allows. If custom UI, locate calendar cells and click dynamically. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>attribute-based locators</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for day/month/year.</t>
+    </r>
+  </si>
+  <si>
+    <t>Calendar handling</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Handle navigation (next/prev month) and select specific dates. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>parameterized locators</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for day values. For range selection, click start date then end date.</t>
+    </r>
+  </si>
+  <si>
+    <t>difference between : test.only(),  test.skip(), test.fail() and test.fixme() - annotations</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">storageState is used to save and reuse browser authentication state, including cookies and local storage data. It helps avoid repeated logins and speeds up test execution.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Save the state after login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : await page.context().</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>storageState</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">({ path: 'auth.json' });
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reuse the state in new tests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 
+const context = await browser.newContext({ storageState: 'auth.json' });
+const page = await context.newPage();
+await page.goto('https://example.com/dashboard'); // already logged in
+or
+test.describe('storageState_Sample', ()=&gt;{
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> test.use({storageState : 'auth.json'});</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    test('testcase1', async({page})=&gt;{
+    launch the url again
+});</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In Playwright, there is no switchToWindow() method like in Selenium. Each browser tab is represented by a Page object. For existing tabs, we can get all open pages using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>context.pages()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and then interact with the required page object directly or bring it to the front using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bringToFront()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Now, context.pages().length only tells you how many tabs are open, like 12, but you can’t switch just by knowing the number. To actually switch, you loop through the pages, check each tab’s URL with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page.url()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and when you find the one you want, you call bringToFront(). So the number is just a count, but page.url() helps identify the right tab to switch to.
+const Total_Pages=context.pages();
+    console.log(`Total number of tabs opened ${Total_Pages.length}`);
+    //loop through "for of loop"
+    for(const p of Total_Pages){
+        console.log(p.url());
+        console.log(await p.title());</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Playwright gives me two ways to handle alerts. With </t>
     </r>
     <r>
@@ -2822,846 +3688,24 @@
 page.on('dialog', async dialog =&gt; {
   console.log('Alert text:', dialog.message());
   await dialog.accept();
-}
-const alertEvent = await page.waitForEvent('dialog');
-await page.getByRole('button', {name : 'submit'}).click();
+});
+const alertEvent = page.waitForEvent('dialog');
+page.getByRole('button', {name : 'submit'}).click();
 const  alert=await alertEvent;
 await alert.accept();
 </t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByRole()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements using their accessibility role (button, textbox, checkbox, link, heading, etc.).
-page.getByRole('button', { name: 'Submit' })
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByText()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements based on visible text.
-page.getByText('Welcome back!')
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByLabel()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates form fields using their label text.
-page.getByLabel('Email address')
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByPlaceholder()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates inputs by their placeholder attribute.
-page.getByPlaceholder('Enter your password')
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByAltText()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements (usually images) by their alt text.
-page.getByAltText('Company logo')
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByTitle()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements by their title attribute.
-page.getByTitle('Close')
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getByTestId()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Locates elements by a data-testid attribute.
-page.getByTestId('login-button')
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>locator()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Generic locator that can use CSS selectors, XPath, and data attributes.
-page.locator('//input[@name="username"]')</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.goto(url)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Navigate to a URL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.reload()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Reload the current page
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.goBack()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Navigate back in history
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.goForward()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Navigate forward in history
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.title()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Get the page title
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.url()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Get the current page URL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.content()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Get the full HTML content of the page
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">page.setContent(html) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">→ Set the page content directly
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.evaluate(fn, arg)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Run JavaScript in the page context
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.pdf(options)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Generate a PDF of the page (Chromium only)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>page.waitForSelector(selector)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Wait until an element appears</t>
-    </r>
-  </si>
-  <si>
-    <t>Button appears after 10 seconds</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>explicit waits</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (WebDriverWait in Selenium / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>page.waitForSelector</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in Playwright) to wait until the button is visible and enabled before interacting. Avoid hard sleeps.</t>
-    </r>
-  </si>
-  <si>
-    <t>Spinner disappears</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Wait for the spinner element to become </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hidden or detached</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Example: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>waitForSelector('.spinner', { state: 'hidden' })</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. This ensures the page is ready for next action.</t>
-    </r>
-  </si>
-  <si>
-    <t>Multiple tabs</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Handle via </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>context switching</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. In Selenium: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>driver.switchTo().window(handle)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. In Playwright: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>context.newPage()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>browserContext.pages()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Always track handles/pages.</t>
-    </r>
-  </si>
-  <si>
-    <t>Multiple users</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Simulate with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>multiple browser contexts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Each context has isolated cookies/storage. In Playwright: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>browser.newContext()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. In Selenium: launch separate driver instances.</t>
-    </r>
-  </si>
-  <si>
-    <t>Dynamic tables</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Identify rows/columns dynamically. Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>XPath/CSS with contains() or nth-child</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Iterate through rows, match cell text, then perform action on sibling/child element.</t>
-    </r>
-  </si>
-  <si>
-    <t>Dynamic XPath</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>functions like contains(), starts-with(), normalize-space()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to handle changing attributes. Example: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>//button[contains(text(),'Submit')]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Avoid brittle absolute paths.</t>
-    </r>
-  </si>
-  <si>
-    <t>Infinite scrolling</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>scroll automation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> until no new elements load. In Playwright: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>page.evaluate(() =&gt; window.scrollBy(0, document.body.scrollHeight))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in a loop with waits.</t>
-    </r>
-  </si>
-  <si>
-    <t>Date picker</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Interact by sending date string if input allows. If custom UI, locate calendar cells and click dynamically. Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>attribute-based locators</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for day/month/year.</t>
-    </r>
-  </si>
-  <si>
-    <t>Calendar handling</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Handle navigation (next/prev month) and select specific dates. Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>parameterized locators</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for day values. For range selection, click start date then end date.</t>
-    </r>
+    <t>dialog.accept()
+dialog.accept('text')
+dialog.dismiss()
+dialog.message()
+dialog.type()
+dialog.defaultValue()</t>
+  </si>
+  <si>
+    <t>Actions that can be performmed on a alert.</t>
   </si>
 </sst>
 </file>
@@ -3754,7 +3798,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3794,9 +3838,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4116,7 +4157,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="43.5">
@@ -4127,7 +4168,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="72.5">
@@ -4138,7 +4179,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="58">
@@ -4149,7 +4190,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29">
@@ -4185,7 +4226,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="72.5" customHeight="1">
+    <row r="9" spans="1:4" ht="233" customHeight="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4193,7 +4234,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="81" customHeight="1">
@@ -4201,10 +4242,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="43.5">
@@ -4212,10 +4253,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="43.5">
@@ -4226,7 +4267,7 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43.5">
@@ -4245,10 +4286,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="72.5">
@@ -4259,7 +4300,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="29">
@@ -4300,10 +4341,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="43.5">
@@ -4311,10 +4352,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -4388,10 +4429,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:4" customFormat="1" ht="58">
@@ -4402,7 +4443,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" customFormat="1" ht="232">
@@ -4410,10 +4451,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:4" customFormat="1" ht="58">
@@ -4446,7 +4487,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:4" customFormat="1" ht="29">
@@ -4468,7 +4509,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" customFormat="1" ht="29">
@@ -4487,10 +4528,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:4" customFormat="1" ht="58">
@@ -4498,10 +4539,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:4" customFormat="1" ht="188.5">
@@ -4509,10 +4550,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:4" customFormat="1" ht="43.5">
@@ -4542,10 +4583,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="188.5">
@@ -4556,7 +4597,7 @@
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:3" customFormat="1">
@@ -4575,10 +4616,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:3" customFormat="1" ht="43.5">
@@ -4589,7 +4630,7 @@
         <v>72</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:3" customFormat="1" ht="72.5">
@@ -4600,7 +4641,7 @@
         <v>35</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3" customFormat="1" ht="29">
@@ -4655,7 +4696,7 @@
         <v>77</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:3" customFormat="1" ht="43.5">
@@ -4677,7 +4718,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:3" customFormat="1" ht="29">
@@ -4721,7 +4762,7 @@
         <v>46</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:3" customFormat="1" ht="58">
@@ -4732,7 +4773,7 @@
         <v>48</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:3" customFormat="1" ht="29">
@@ -4776,7 +4817,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" customFormat="1" ht="43.5">
@@ -4787,7 +4828,7 @@
         <v>84</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:3" customFormat="1" ht="72.5">
@@ -4798,7 +4839,7 @@
         <v>85</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:3" customFormat="1">
@@ -4806,10 +4847,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:3" customFormat="1" ht="217.5">
@@ -4817,10 +4858,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -4855,10 +4896,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4896,7 +4937,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29">
@@ -4904,10 +4945,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="43.5">
@@ -4937,10 +4978,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -4975,10 +5016,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -4988,7 +5029,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6422BD2A-921C-4791-9418-7944EF57C8A1}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
@@ -5016,7 +5057,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="130.5">
@@ -5024,13 +5065,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="87">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="226.5" customHeight="1">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -5038,7 +5079,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="43.5">
@@ -5046,10 +5087,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="87">
@@ -5057,21 +5098,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="290">
+    </row>
+    <row r="7" spans="1:4" ht="324.5" customHeight="1">
       <c r="A7" s="11">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="174">
@@ -5079,10 +5120,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="217.5">
@@ -5090,21 +5131,32 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="319">
-      <c r="A10" s="14">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>154</v>
+      <c r="B10" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="97.5" customHeight="1">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -5172,10 +5224,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29">
@@ -5183,10 +5235,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29">
@@ -5194,10 +5246,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="29">
@@ -5205,10 +5257,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="29">
@@ -5216,10 +5268,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29">
@@ -5227,10 +5279,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="29">
@@ -5238,10 +5290,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="29">
@@ -5249,10 +5301,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29">
@@ -5260,10 +5312,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/Interview questions.xlsx
+++ b/Interview questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonlinenam-my.sharepoint.com/personal/910388_cognizant_com/Documents/Desktop/Playwright/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{AC0EBE63-7BE9-4985-87B0-7EEEAB2A6DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04903C3E-5143-4B8F-9C4B-1B8831347FB6}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{AC0EBE63-7BE9-4985-87B0-7EEEAB2A6DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42D5740C-79DB-442D-B40E-BA37D3A93229}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Playwright Basics" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <sheet name="Testing" sheetId="13" r:id="rId10"/>
     <sheet name="Git" sheetId="14" r:id="rId11"/>
     <sheet name="CICD" sheetId="15" r:id="rId12"/>
-    <sheet name="Sheet5" sheetId="16" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Locators!$A$1:$D$42</definedName>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="203">
   <si>
     <t>No</t>
   </si>
@@ -393,99 +392,6 @@
   </si>
   <si>
     <t>In Playwright, you configure default wait times in playwright.config.ts using actionTimeout, expect.timeout, or the global timeout for tests. This way you don’t need to set timeouts manually in every test.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Hooks in Playwright are used for common setup and teardown logic around test execution. There are four hooks:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>beforeAll</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Runs once before all tests in a file.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>afterAll</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Runs once after all tests in a file.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>beforeEach</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Runs before every individual test.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>afterEach</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Runs after every individual test.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -873,125 +779,6 @@
     <t>How do you pass keyboard keys?</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>locatot.press()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is useful for testing keyboard interactions and shortcuts.
-await input.press('Backspace');
-await input.press('Control+A');
-await page.locator('#input').press('Control+Alt+Delete');</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">locator.waitFor() is a generic waiting method that lets you pause until a specific condition on an element is met.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">attached </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">→ Waits until the element is present in the DOM.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>detached</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Waits until the element is removed from the DOM.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>visible</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Waits until the element is visible (not hidden and has non‑zero size).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hidden</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Waits until the element is either detached or has display:none/visibility:hidden.</t>
-    </r>
-  </si>
-  <si>
     <t>List all the toHave() assertions.</t>
   </si>
   <si>
@@ -1349,10 +1136,6 @@
   </si>
   <si>
     <t>How to manage baselines?</t>
-  </si>
-  <si>
-    <t>Playwright manages baselines itself, but you can update them when your UI intentionally changes.
-npx playwright test --update-snapshots</t>
   </si>
   <si>
     <t>Page methods()</t>
@@ -1919,9 +1702,6 @@
   </si>
   <si>
     <t>Upload Files - Single file</t>
-  </si>
-  <si>
-    <t>Upload Files - Double file</t>
   </si>
   <si>
     <t xml:space="preserve">Using setInputFiles('file path'); Directly uploads the specified file.
@@ -2165,9 +1945,6 @@
       </rPr>
       <t xml:space="preserve"> → returns the filename suggested by the server.</t>
     </r>
-  </si>
-  <si>
-    <t>Playwright APIs are asynchronous because they interact with the browser. You use await to ensure each action completes before moving on. Synchronous code runs line by line and blocks, while async code in Playwright returns promises and allows non‑blocking execution. This design makes tests stable and prevents race conditions</t>
   </si>
   <si>
     <t>hard assert and soft assert?</t>
@@ -3062,29 +2839,32 @@
     <t>Button appears after 10 seconds</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>explicit waits</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (WebDriverWait in Selenium / </t>
+    <t>Spinner disappears</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wait for the spinner element to become </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hidden or detached</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Example: </t>
     </r>
     <r>
       <rPr>
@@ -3092,53 +2872,6 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>page.waitForSelector</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in Playwright) to wait until the button is visible and enabled before interacting. Avoid hard sleeps.</t>
-    </r>
-  </si>
-  <si>
-    <t>Spinner disappears</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Wait for the spinner element to become </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hidden or detached</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Example: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
       <t>waitForSelector('.spinner', { state: 'hidden' })</t>
     </r>
     <r>
@@ -3154,86 +2887,6 @@
   </si>
   <si>
     <t>Multiple tabs</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Handle via </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>context switching</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. In Selenium: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>driver.switchTo().window(handle)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. In Playwright: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>context.newPage()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>browserContext.pages()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Always track handles/pages.</t>
-    </r>
   </si>
   <si>
     <t>Multiple users</t>
@@ -3706,6 +3359,675 @@
   </si>
   <si>
     <t>Actions that can be performmed on a alert.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hooks in Playwright are used for common setup and teardown logic around test execution. There are four hooks:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>beforeAll</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Runs once before all tests in a file. Setup test data. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>afterAll</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Runs once after all tests in a file. Cleanup test data
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>beforeEach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Runs before every individual test. Login before test
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>afterEach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Runs after every individual test. Clear test state</t>
+    </r>
+  </si>
+  <si>
+    <t>pom</t>
+  </si>
+  <si>
+    <t>Synchronous execution means tasks run one after another, and the next task waits until the current task is completed. Asynchronous execution means a task can start and, while it's waiting for a response, other tasks can continue without blocking the application.</t>
+  </si>
+  <si>
+    <t>Upload Files - Multiple files</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>locator.press()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is useful for testing keyboard interactions and shortcuts.
+await input.press('Backspace');
+await input.press('Control+A');
+await page.locator('#input').press('Control+Alt+Delete');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">locator.waitFor() is a generic waiting method that lets you pause until a specific condition on an element is met.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">attached </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">→ Waits until the element is present in the DOM.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>detached</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Waits until the element is removed from the DOM.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>visible</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Waits until the element is visible (not hidden and has non‑zero size).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hidden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Waits until the element is either detached or has display:none/visibility:hidden.
+await locator.waitFor({ state: 'attached' }); // Present in DOM
+await locator.waitFor({ state: 'detached' }); // Removed from DOM
+await locator.waitFor({ state: 'visible' });  // Visible to user
+await locator.waitFor({ state: 'hidden' });   // Hidden or removed</t>
+    </r>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>HTTP Methods</t>
+  </si>
+  <si>
+    <t>Status Codes</t>
+  </si>
+  <si>
+    <t>Headers</t>
+  </si>
+  <si>
+    <t>Headers provide extra information. Content-Type (Indicates JSON data.), Authorization(Used for authentication)</t>
+  </si>
+  <si>
+    <t>Request Body</t>
+  </si>
+  <si>
+    <t>Used mainly in POST, PUT, PATCH.</t>
+  </si>
+  <si>
+    <t>JSON Basics</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Most APIs are protected. 
+Basic Auth(username/password)
+Bearer Token(Authorization: Bearer eyJhbGci..)
+Oauth(Client ID, Client Secret, Access Token)</t>
+  </si>
+  <si>
+    <t>What is REST API?</t>
+  </si>
+  <si>
+    <t>API stands for Application Programming Interface. Communication medium between applications.</t>
+  </si>
+  <si>
+    <t>GET - retrieves data.
+POST - creates data.
+PUT - updates complete resource.
+PATCH - updates partial resource.
+DELETE - deletes resource.</t>
+  </si>
+  <si>
+    <r>
+      <t>Data exchange format used in APIs.
+Types :
+{
+  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": "Hello",
+  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": 25,
+  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>boolean</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": true,
+  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>array</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": [1, 2, 3],
+  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": {
+    "city": "Chennai"
+  }
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">REST = Representational State Transfer. Most APIs today are REST APIs.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HTTP-based stateless API architecture.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Characteristics:
+Client Server Architecture
+Stateless
+Uses HTTP methods
+JSON response</t>
+    </r>
+  </si>
+  <si>
+    <t>Bearer Token?</t>
+  </si>
+  <si>
+    <t>Token-based authentication mechanism.</t>
+  </si>
+  <si>
+    <t>200 - Success
+201 - Created (usually used with POST)
+204 - Success but no response body.
+400 - Bad Request
+401 - Unauthorized - No token, Invalid token, expired token.
+403 - Forbidden - The user is authenticated (identity is known), but does not have permission to access that resource.
+404 - Not Found
+500 - Internal Server Error
+504 - Timeout Error</t>
+  </si>
+  <si>
+    <t>page.waitForSelector(selector) is used to wait until an element reaches a specified state (visible, attached, hidden, or detached) before performing actions on it. However, Playwright recommends using locators because they provide automatic waiting.</t>
+  </si>
+  <si>
+    <t>how do you wait for a selector?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A baseline usually refers to the reference screenshot used in visual testing.
+await expect(page).toHaveScreenshot('homepage.png');
+Playwright manages baselines itself, but you can update them when your UI intentionally changes.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>npx playwright test --update-snapshots</t>
+    </r>
+  </si>
+  <si>
+    <t>Implicit wait is a global wait applied to all element searches, whereas explicit wait is used for specific elements or conditions. Playwright does not have implicit waits and mainly relies on auto-waiting and explicit waits when required</t>
+  </si>
+  <si>
+    <t>implicit wait vs Explict wait?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>project structure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+project
+│
+├── pages
+│ └── LoginPage.js
+│
+└── tests
+└── login.spec.js
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LoginPage.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+class LoginPage {
+    constructor(page) {
+        this.page = page;
+    }
+    async login(username, password) {
+        await this.page.fill('#username', username);
+        await this.page.fill('#password', password);
+        await this.page.click('#loginBtn');
+    }
+}
+module.exports = LoginPage;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Login.spec.js
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>const { test } = require('@playwright/test');
+const LoginPage = require('../pages/LoginPage');
+test('Login Test', async ({ page }) =&gt; {
+    await page.goto('https://example.com');
+    const loginPage = new LoginPage(page);
+    await loginPage.login('admin', 'password');
+});</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>explicit waits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>page.waitForSelector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Playwright) to wait until the button is visible and enabled before interacting. Avoid hard sleeps.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Handle via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>context switching</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. In Playwright: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>context.newPage()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>browserContext.pages()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Always track handles/pages.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3771,7 +4093,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3794,11 +4116,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3839,8 +4172,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4127,7 +4478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="9"/>
@@ -4168,7 +4519,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="72.5">
@@ -4179,7 +4530,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="58">
@@ -4190,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29">
@@ -4234,7 +4585,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="81" customHeight="1">
@@ -4242,10 +4593,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="43.5">
@@ -4253,7 +4604,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>100</v>
@@ -4281,15 +4632,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="29">
+    <row r="14" spans="1:4" ht="58">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="72.5">
@@ -4300,7 +4651,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="29">
@@ -4341,10 +4692,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="43.5">
@@ -4352,10 +4703,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="29">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4391,15 +4753,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975AD39B-1C4B-4DE0-8AD9-C324340E2C67}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{913B1BA8-DC3A-4E90-879B-767360794D4C}">
   <dimension ref="A1:D41"/>
@@ -4454,7 +4807,7 @@
         <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:4" customFormat="1" ht="58">
@@ -4487,7 +4840,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:4" customFormat="1" ht="29">
@@ -4509,7 +4862,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:4" customFormat="1" ht="29">
@@ -4539,10 +4892,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:4" customFormat="1" ht="188.5">
@@ -4550,10 +4903,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:4" customFormat="1" ht="43.5">
@@ -4597,7 +4950,7 @@
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:3" customFormat="1">
@@ -4616,10 +4969,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:3" customFormat="1" ht="43.5">
@@ -4633,7 +4986,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="72.5">
+    <row r="21" spans="1:3" customFormat="1" ht="130.5">
       <c r="A21" s="11">
         <v>20</v>
       </c>
@@ -4641,7 +4994,7 @@
         <v>35</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:3" customFormat="1" ht="29">
@@ -4762,7 +5115,7 @@
         <v>46</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:3" customFormat="1" ht="58">
@@ -4847,10 +5200,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:3" customFormat="1" ht="217.5">
@@ -4858,10 +5211,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4896,10 +5249,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4909,7 +5262,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B9138F-152F-47B5-A715-13A6525B10BB}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
@@ -4937,7 +5290,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29">
@@ -4978,10 +5331,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>140</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.5">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -5016,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -5057,7 +5421,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="130.5">
@@ -5065,10 +5429,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="226.5" customHeight="1">
@@ -5079,7 +5443,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="43.5">
@@ -5087,10 +5451,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="87">
@@ -5098,10 +5462,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="324.5" customHeight="1">
@@ -5109,10 +5473,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="174">
@@ -5120,10 +5484,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="217.5">
@@ -5131,10 +5495,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="319">
@@ -5142,21 +5506,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="97.5" customHeight="1">
       <c r="A11" s="11">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>178</v>
+      <c r="B11" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -5166,7 +5530,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308F6E79-B2D5-41F4-AD37-A7BE9FF5DB5F}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="46.81640625" customWidth="1"/>
@@ -5224,10 +5588,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29">
@@ -5235,21 +5599,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="29">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="23" customHeight="1">
       <c r="A7" s="11">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="29">
@@ -5257,10 +5621,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="29">
@@ -5268,10 +5632,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29">
@@ -5279,10 +5643,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="29">
@@ -5290,10 +5654,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="29">
@@ -5301,10 +5665,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29">
@@ -5312,11 +5676,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="409.5" customHeight="1">
+      <c r="A14" s="20">
+        <v>13</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>172</v>
       </c>
+      <c r="C14" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5325,9 +5703,126 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81243443-8543-49DE-8D13-ABDA6A090A9E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="46.81640625" customWidth="1"/>
+    <col min="3" max="3" width="102.26953125" customWidth="1"/>
+    <col min="4" max="4" width="61.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="8" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72.5">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="130.5">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="159.5">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="58">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="101.5">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
